--- a/test/A1_B4_52_PRANAV_RATHI_TESTCASES.xlsx
+++ b/test/A1_B4_52_PRANAV_RATHI_TESTCASES.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>30 09 2026</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>1</v>
       </c>
@@ -686,7 +686,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>2</v>
       </c>
@@ -734,7 +734,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>3</v>
       </c>
@@ -750,9 +750,9 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Product: Laptop
-Product ID: WMS-101
-Qty: 25</t>
+          <t>Product: Keyboard
+Product ID: P001
+Qty: 20</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>4</v>
       </c>
@@ -801,7 +801,7 @@
       <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Product Name: blank
-Product ID: WMS-102</t>
+Product ID: P002</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -832,7 +832,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>5</v>
       </c>
@@ -843,91 +843,91 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
+          <t>Add product with existing ID</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Product ID: P001</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>P001 already exists</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>1. Open Add Product
+2. Enter Product ID P001
+3. Click Save</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Duplicate Product ID should not be accepted.</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Duplicate Product ID message was shown.</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>TC_006</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
           <t>Add product with empty Product ID</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Product ID: blank
 Name: iPhone 16 Pro</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Add Product page is open</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>1. Leave Product ID empty
 2. Enter name
 3. Click Save</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>System should ask for Product ID.</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Product ID required message was shown.</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>TC_006</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Add product with duplicate ID</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Product ID: WMS-101
-(Already exists)</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>WMS-101 already exists</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>1. Enter existing Product ID WMS-101
-2. Click Save</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Duplicate Product ID should not be accepted.</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Duplicate Product ID message was shown.</t>
-        </is>
-      </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="34" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>7</v>
       </c>
@@ -974,7 +974,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>8</v>
       </c>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="34" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>9</v>
       </c>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="34" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>10</v>
       </c>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="34" customHeight="1">
       <c r="A19" s="6" t="n">
         <v>11</v>
       </c>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="34" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>12</v>
       </c>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="34" customHeight="1">
       <c r="A21" s="6" t="n">
         <v>13</v>
       </c>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="34" customHeight="1">
       <c r="A22" s="6" t="n">
         <v>14</v>
       </c>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="34" customHeight="1">
       <c r="A23" s="6" t="n">
         <v>15</v>
       </c>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="6" t="n">
         <v>16</v>
       </c>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="34" customHeight="1">
       <c r="A25" s="6" t="n">
         <v>17</v>
       </c>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="36" customHeight="1">
+    <row r="26" ht="34" customHeight="1">
       <c r="A26" s="6" t="n">
         <v>18</v>
       </c>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="6" t="n">
         <v>19</v>
       </c>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="36" customHeight="1">
+    <row r="28" ht="34" customHeight="1">
       <c r="A28" s="6" t="n">
         <v>20</v>
       </c>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="36" customHeight="1">
+    <row r="29" ht="34" customHeight="1">
       <c r="A29" s="6" t="n">
         <v>21</v>
       </c>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="36" customHeight="1">
+    <row r="30" ht="34" customHeight="1">
       <c r="A30" s="6" t="n">
         <v>22</v>
       </c>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="36" customHeight="1">
+    <row r="31" ht="34" customHeight="1">
       <c r="A31" s="6" t="n">
         <v>23</v>
       </c>
@@ -1719,7 +1719,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="36" customHeight="1">
+    <row r="32" ht="34" customHeight="1">
       <c r="A32" s="6" t="n">
         <v>24</v>
       </c>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="36" customHeight="1">
+    <row r="33" ht="34" customHeight="1">
       <c r="A33" s="6" t="n">
         <v>25</v>
       </c>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="36" customHeight="1">
+    <row r="34" ht="34" customHeight="1">
       <c r="A34" s="6" t="n">
         <v>26</v>
       </c>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="36" customHeight="1">
+    <row r="35" ht="34" customHeight="1">
       <c r="A35" s="6" t="n">
         <v>27</v>
       </c>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="36" customHeight="1">
+    <row r="36" ht="34" customHeight="1">
       <c r="A36" s="6" t="n">
         <v>28</v>
       </c>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="36" customHeight="1">
+    <row r="37" ht="34" customHeight="1">
       <c r="A37" s="6" t="n">
         <v>29</v>
       </c>
@@ -1993,7 +1993,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="36" customHeight="1">
+    <row r="38" ht="34" customHeight="1">
       <c r="A38" s="6" t="n">
         <v>30</v>
       </c>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>30 09 2026</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>1</v>
       </c>
@@ -2200,34 +2200,35 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Test Product model getters and setters</t>
+          <t>Verify getter and setter statement coverage</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Product.java
-getters/setters</t>
+          <t>Product ID: WMS-101
+Name: MacBook Pro</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Valid model fields</t>
+          <t>Product class is available</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>1. Set field values
-2. Call getters</t>
+          <t>1. Instantiate Product
+2. Set field values
+3. Call getters</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Values should be preserved without corruption.</t>
+          <t>Getter methods should return assigned values.</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Values preserved correctly.</t>
+          <t>Getter methods returned assigned values.</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -2236,7 +2237,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>2</v>
       </c>
@@ -2247,33 +2248,32 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Test toJson() with null description</t>
+          <t>Verify toJson() branch with null description</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Product.java
-toJson()</t>
+          <t>Description: null</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>description == null</t>
+          <t>Product created with null description</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>1. Pass product with null description to toJson()</t>
+          <t>1. Call toJson() on product</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>JSON should contain null description without exception.</t>
+          <t>JSON should contain null description without crash.</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>JSON rendered safely.</t>
+          <t>JSON rendered safely without exception.</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
@@ -2282,7 +2282,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>3</v>
       </c>
@@ -2293,33 +2293,32 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Test toJson() with valid description</t>
+          <t>Verify toJson() branch with valid description</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Product.java
-toJson()</t>
+          <t>Description: Flagship laptop</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>description != null</t>
+          <t>Product has valid description</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>1. Pass valid description to toJson()</t>
+          <t>1. Call toJson() on product</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Description should be quoted in JSON.</t>
+          <t>Description should be quoted in JSON output.</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Description quoted properly.</t>
+          <t>Description was quoted properly.</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -2328,7 +2327,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>4</v>
       </c>
@@ -2339,18 +2338,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Test escapeJson() with null string</t>
+          <t>Verify escapeJson() handling null input</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Product.java
-escapeJson()</t>
+          <t>Input: null</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>str == null</t>
+          <t>Product model loaded</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -2365,7 +2363,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Empty string returned.</t>
+          <t>Empty string was returned.</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
@@ -2374,7 +2372,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>5</v>
       </c>
@@ -2385,33 +2383,32 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Test escapeJson() with double quotes</t>
+          <t>Verify escapeJson() escaping double quotes</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Product.java
-escapeJson()</t>
+          <t>Input: 16" Screen</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>str = '16" Laptop'</t>
+          <t>String contains double quotes</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>1. Pass string with quotes</t>
+          <t>1. Call escapeJson()</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Quotes should be escaped to \".</t>
+          <t>Quotes should be escaped properly.</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Quotes escaped properly.</t>
+          <t>Quotes were escaped properly.</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
@@ -2420,7 +2417,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>6</v>
       </c>
@@ -2431,33 +2428,32 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Test escapeJson() with backslash</t>
+          <t>Verify escapeJson() escaping backslashes</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Product.java
-escapeJson()</t>
+          <t>Input: Path\Folder</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>str = 'Path\\Item'</t>
+          <t>String contains backslash</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>1. Pass string with backslash</t>
+          <t>1. Call escapeJson()</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Backslash should be escaped to \\\\.</t>
+          <t>Backslash should be escaped properly.</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Backslash escaped properly.</t>
+          <t>Backslash was escaped properly.</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -2466,7 +2462,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="34" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>7</v>
       </c>
@@ -2477,18 +2473,17 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Test price decimal formatting</t>
+          <t>Verify price decimal formatting in toJson()</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Product.java
-toJson()</t>
+          <t>unitPrice: 1999.5</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>unitPrice = 1499.5</t>
+          <t>Product has decimal price</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -2512,7 +2507,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>8</v>
       </c>
@@ -2523,18 +2518,17 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Test UTF-8 JSON response headers</t>
+          <t>Verify sendJson() HTTP response header</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>HttpUtil.java
-sendJson()</t>
+          <t>Status: 200</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>HttpServletResponse</t>
+          <t>HttpServletResponse active</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -2544,12 +2538,12 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Header should be application/json;charset=UTF-8.</t>
+          <t>Content-Type header should be application/json.</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Header set correctly.</t>
+          <t>Header was set correctly.</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
@@ -2558,7 +2552,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="34" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>9</v>
       </c>
@@ -2569,18 +2563,18 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Test error JSON schema format</t>
+          <t>Verify sendError() JSON payload structure</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>HttpUtil.java
-sendError()</t>
+          <t>Status: 400
+Message: Invalid input</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>statusCode = 400</t>
+          <t>HttpServletResponse active</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -2595,7 +2589,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Error JSON generated.</t>
+          <t>Error JSON was generated.</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
@@ -2604,7 +2598,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="34" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>10</v>
       </c>
@@ -2615,33 +2609,32 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Test readRequestBody() with valid body</t>
+          <t>Verify readRequestBody() reading stream</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>HttpUtil.java
-readRequestBody()</t>
+          <t>JSON: {"name":"iPhone 16"}</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>InputStream with JSON</t>
+          <t>Request stream active</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>1. Read JSON stream</t>
+          <t>1. Call readRequestBody()</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Should return complete body string.</t>
+          <t>Complete request body should be read.</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Body string returned.</t>
+          <t>Request body was read accurately.</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
@@ -2650,7 +2643,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="34" customHeight="1">
       <c r="A19" s="6" t="n">
         <v>11</v>
       </c>
@@ -2661,23 +2654,22 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Test readRequestBody() with empty body</t>
+          <t>Verify readRequestBody() empty stream</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>HttpUtil.java
-readRequestBody()</t>
+          <t>Input stream: Empty</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Empty stream</t>
+          <t>Request stream empty</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>1. Read empty stream</t>
+          <t>1. Call readRequestBody()</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -2687,7 +2679,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Empty string returned.</t>
+          <t>Empty string was returned.</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
@@ -2696,7 +2688,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="34" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>12</v>
       </c>
@@ -2707,33 +2699,32 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Test parseParameters() URL-encoded form</t>
+          <t>Verify parseParameters() URL-encoded form</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>HttpUtil.java
-parseParameters()</t>
+          <t>Query: action=add&amp;qty=5</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>action=add&amp;qty=5</t>
+          <t>URL-encoded query received</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>1. Parse query string</t>
+          <t>1. Call parseParameters()</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Map should contain key-value pairs.</t>
+          <t>Map should contain parsed key-value pairs.</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Map parsed properly.</t>
+          <t>Map was populated with parameters.</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
@@ -2742,7 +2733,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="34" customHeight="1">
       <c r="A21" s="6" t="n">
         <v>13</v>
       </c>
@@ -2753,33 +2744,32 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Test DBConnection environment variable URL</t>
+          <t>Verify DBConnection environment variable URL</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>DBConnection.java
-init()</t>
+          <t>Env: WMS_DB_URL set</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>WMS_DB_URL set</t>
+          <t>Environment variable set</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>1. Check env variable</t>
+          <t>1. Call DBConnection.init()</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Connection should use environment URL.</t>
+          <t>Connection should use environment variable URL.</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Environment URL used.</t>
+          <t>Environment URL was used.</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
@@ -2788,7 +2778,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="34" customHeight="1">
       <c r="A22" s="6" t="n">
         <v>14</v>
       </c>
@@ -2799,33 +2789,32 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Test DBConnection properties fallback</t>
+          <t>Verify DBConnection properties fallback</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>DBConnection.java
-init()</t>
+          <t>Env: WMS_DB_URL=null</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>db.properties file</t>
+          <t>Environment variable not set</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>1. Check properties file</t>
+          <t>1. Call DBConnection.init()</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Should read from db.properties.</t>
+          <t>Configuration should load from db.properties.</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Read from properties file.</t>
+          <t>Loaded from db.properties.</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
@@ -2834,7 +2823,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="34" customHeight="1">
       <c r="A23" s="6" t="n">
         <v>15</v>
       </c>
@@ -2845,33 +2834,32 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Test DBConnection missing config check</t>
+          <t>Verify DBConnection missing config check</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>DBConnection.java
-init()</t>
+          <t>Config: All properties null</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>url == null</t>
+          <t>No DB config provided</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>1. Initialize without config</t>
+          <t>1. Call DBConnection.init()</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Should throw RuntimeException.</t>
+          <t>RuntimeException should be thrown.</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>RuntimeException thrown.</t>
+          <t>RuntimeException was thrown.</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
@@ -2880,7 +2868,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="6" t="n">
         <v>16</v>
       </c>
@@ -2891,18 +2879,17 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Test DBConnection singleton caching</t>
+          <t>Verify DBConnection singleton reuse</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>DBConnection.java
-getConnection()</t>
+          <t>Database connection request</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>initialized == true</t>
+          <t>Connection initialized</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -2912,12 +2899,12 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Should reuse cached configuration.</t>
+          <t>Cached configuration should be reused.</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Cached config reused.</t>
+          <t>Cached config was reused.</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
@@ -2926,7 +2913,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="34" customHeight="1">
       <c r="A25" s="6" t="n">
         <v>17</v>
       </c>
@@ -2937,33 +2924,32 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Test createProduct() SQL parameter binding</t>
+          <t>Verify createProduct() SQL parameter binding</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-createProduct()</t>
+          <t>Product: WMS-105, Price: 24900</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>PreparedStatement</t>
+          <t>Database connection open</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>1. Bind parameters 1 to 6</t>
+          <t>1. Call createProduct()</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>SQL parameters should bind safely without injection.</t>
+          <t>PreparedStatement parameters 1-6 should bind safely.</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Parameters bound safely.</t>
+          <t>Parameters were bound safely.</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
@@ -2972,7 +2958,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="36" customHeight="1">
+    <row r="26" ht="34" customHeight="1">
       <c r="A26" s="6" t="n">
         <v>18</v>
       </c>
@@ -2983,18 +2969,17 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Test createProduct() duplicate key handling</t>
+          <t>Verify createProduct() duplicate key handling</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-createProduct()</t>
+          <t>Product ID: WMS-101 (Duplicate)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Vendor code 1062</t>
+          <t>ID already exists</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -3004,12 +2989,12 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Should catch error 1062 and throw conflict.</t>
+          <t>Duplicate key error 1062 should be caught.</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Duplicate key caught.</t>
+          <t>Duplicate key error was caught.</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -3018,7 +3003,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="6" t="n">
         <v>19</v>
       </c>
@@ -3029,33 +3014,32 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Test getAllProducts() with empty table</t>
+          <t>Verify getAllProducts() empty table handling</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-getAllProducts()</t>
+          <t>Database table: products (0 rows)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>rs.next() == false</t>
+          <t>Table is empty</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>1. Query empty table</t>
+          <t>1. Query products table</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Should return empty list with size 0.</t>
+          <t>Should return empty List with size 0.</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Empty list returned.</t>
+          <t>Empty List returned.</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
@@ -3064,7 +3048,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="36" customHeight="1">
+    <row r="28" ht="34" customHeight="1">
       <c r="A28" s="6" t="n">
         <v>20</v>
       </c>
@@ -3075,33 +3059,32 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Test getAllProducts() loop iteration</t>
+          <t>Verify getAllProducts() cursor mapping loop</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-getAllProducts()</t>
+          <t>Database table: products (7 rows)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>rs.next() == true</t>
+          <t>Table has 7 rows</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>1. Loop through cursor</t>
+          <t>1. Query products table</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>All rows should map into Product objects.</t>
+          <t>Loop should map all 7 rows to Product objects.</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>All rows mapped properly.</t>
+          <t>All 7 rows mapped properly.</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -3110,7 +3093,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="36" customHeight="1">
+    <row r="29" ht="34" customHeight="1">
       <c r="A29" s="6" t="n">
         <v>21</v>
       </c>
@@ -3121,33 +3104,32 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Test getProductById() row found</t>
+          <t>Verify getProductById() branch when record exists</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-getProductById()</t>
+          <t>Query ID: WMS-101</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Row found in DB</t>
+          <t>WMS-101 exists in DB</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>1. Query valid ID</t>
+          <t>1. Query WMS-101</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Should return populated Product object.</t>
+          <t>Populated Product object should be returned.</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Populated object returned.</t>
+          <t>Populated Product was returned.</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
@@ -3156,7 +3138,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="36" customHeight="1">
+    <row r="30" ht="34" customHeight="1">
       <c r="A30" s="6" t="n">
         <v>22</v>
       </c>
@@ -3167,33 +3149,32 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Test getProductById() row not found</t>
+          <t>Verify getProductById() branch when not found</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-getProductById()</t>
+          <t>Query ID: GHOST-999</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Row not found</t>
+          <t>ID does not exist</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>1. Query unknown ID</t>
+          <t>1. Query GHOST-999</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Should return null safely.</t>
+          <t>Null should be returned safely.</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Null returned safely.</t>
+          <t>Null was returned safely.</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -3202,7 +3183,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="36" customHeight="1">
+    <row r="31" ht="34" customHeight="1">
       <c r="A31" s="6" t="n">
         <v>23</v>
       </c>
@@ -3213,33 +3194,33 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Test updateProduct() SQL execution</t>
+          <t>Verify updateProduct() SQL execution</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-updateProduct()</t>
+          <t>Product ID: WMS-104
+New Price: 34500</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>UPDATE query</t>
+          <t>WMS-104 exists in DB</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>1. Execute update</t>
+          <t>1. Call updateProduct()</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Row count should be returned.</t>
+          <t>Affected row count &gt; 0 should be returned.</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>Row count returned.</t>
+          <t>Row count 1 was returned.</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
@@ -3248,7 +3229,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="36" customHeight="1">
+    <row r="32" ht="34" customHeight="1">
       <c r="A32" s="6" t="n">
         <v>24</v>
       </c>
@@ -3259,33 +3240,32 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Test updateProduct() 0 rows affected</t>
+          <t>Verify updateProduct() 0 rows affected branch</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-updateProduct()</t>
+          <t>Product ID: NON-EXIST-888</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>rowsAffected == 0</t>
+          <t>ID does not exist</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>1. Update non-existent SKU</t>
+          <t>1. Call updateProduct()</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>Should return null.</t>
+          <t>Should return null for non-existent product.</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Null returned.</t>
+          <t>Null was returned.</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -3294,7 +3274,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="36" customHeight="1">
+    <row r="33" ht="34" customHeight="1">
       <c r="A33" s="6" t="n">
         <v>25</v>
       </c>
@@ -3305,33 +3285,33 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Test addStock() row locking query</t>
+          <t>Verify addStock() pessimistic row-locking</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-addStock()</t>
+          <t>Product ID: WMS-101
+Quantity: 10</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>SELECT ... FOR UPDATE</t>
+          <t>Active transaction</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>1. Execute query</t>
+          <t>1. Execute SELECT ... FOR UPDATE</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Pessimistic row lock should be placed.</t>
+          <t>InnoDB row lock should be placed.</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Row lock acquired.</t>
+          <t>Row lock was acquired.</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
@@ -3340,7 +3320,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="36" customHeight="1">
+    <row r="34" ht="34" customHeight="1">
       <c r="A34" s="6" t="n">
         <v>26</v>
       </c>
@@ -3351,23 +3331,23 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Test addStock() commit execution</t>
+          <t>Verify addStock() atomic commit execution</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-addStock()</t>
+          <t>Current: 25, Add: 10</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>conn.commit()</t>
+          <t>Row lock acquired</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>1. Increment quantity</t>
+          <t>1. Execute UPDATE
+2. Call conn.commit()</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -3377,7 +3357,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Transaction committed.</t>
+          <t>Transaction committed successfully.</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
@@ -3386,7 +3366,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="36" customHeight="1">
+    <row r="35" ht="34" customHeight="1">
       <c r="A35" s="6" t="n">
         <v>27</v>
       </c>
@@ -3397,13 +3377,12 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Test reduceStock() over-reduction check</t>
+          <t>Verify reduceStock() decision on excess quantity</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-reduceStock()</t>
+          <t>Current: 10, Reduce: 50</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -3413,17 +3392,17 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>1. Try to reduce excess quantity</t>
+          <t>1. Try to reduce 50 from 10</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Should call conn.rollback() and throw exception.</t>
+          <t>Rollback should occur and exception thrown.</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>Rollback executed safely.</t>
+          <t>Rollback occurred; exception thrown.</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -3432,7 +3411,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="36" customHeight="1">
+    <row r="36" ht="34" customHeight="1">
       <c r="A36" s="6" t="n">
         <v>28</v>
       </c>
@@ -3443,18 +3422,17 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Test reduceStock() rollback in catch</t>
+          <t>Verify reduceStock() rollback in catch block</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-reduceStock()</t>
+          <t>Simulated SQL exception</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>SQLException occurs</t>
+          <t>Database error during decrement</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -3469,7 +3447,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Rollback called in catch.</t>
+          <t>Rollback called in catch block.</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
@@ -3478,7 +3456,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="36" customHeight="1">
+    <row r="37" ht="34" customHeight="1">
       <c r="A37" s="6" t="n">
         <v>29</v>
       </c>
@@ -3489,13 +3467,12 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Test reduceStock() normal reduction</t>
+          <t>Verify reduceStock() normal reduction branch</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-reduceStock()</t>
+          <t>Current: 36, Reduce: 5</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -3505,7 +3482,7 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>1. Reduce valid quantity</t>
+          <t>1. Reduce valid quantity 5</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -3515,7 +3492,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>Decremented and committed.</t>
+          <t>Quantity decremented and committed.</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
@@ -3524,7 +3501,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="36" customHeight="1">
+    <row r="38" ht="34" customHeight="1">
       <c r="A38" s="6" t="n">
         <v>30</v>
       </c>
@@ -3535,33 +3512,32 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Test connection close in finally block</t>
+          <t>Verify resource cleanup in finally block</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>ProductDAO.java
-reduceStock()</t>
+          <t>Connection and Statements</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>finally block</t>
+          <t>DAO operation complete</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>1. Complete execution</t>
+          <t>1. Enter finally block</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>Connection must be closed in finally block.</t>
+          <t>All JDBC resources must be closed safely.</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>Connection closed in finally.</t>
+          <t>All resources closed in finally.</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
